--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-13_Data_Migration_v1.2.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-13_Data_Migration_v1.2.xlsx
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>From FRS BRD-13 v1.1 - cases for FR-DM-034 (package remapping) and FR-DM-124 (carried renewals of the January-May 2028 expiries), the mock-load order (FR-DM-120), the sign of a Migration Clearing difference (FR-DM-021), the excluded rows in the error rate (FR-DM-013), MIG_UPP_ISSUE_AR (FR-DM-051), QPS invoice numbers before DMQ11 (FR-DM-061) and the quoted messages of FR-DM-091, 110 and 123; test levels on the BDOI timeline; the seven findings of v1.0 are resolved in the FRS</t>
+          <t>From FRS BRD-13 v1.1 - cases for FR-DM-034 (package remapping) and FR-DM-124 (carried renewals of the January-May 2028 expiries), the trial-migration load order (FR-DM-120), the sign of a Migration Clearing difference (FR-DM-021), the excluded rows in the error rate (FR-DM-013), MIG_UPP_ISSUE_AR (FR-DM-051), QPS invoice numbers before DMQ11 (FR-DM-061) and the quoted messages of FR-DM-091, 110 and 123; test levels on the BDOI timeline; the seven findings of v1.0 are resolved in the FRS</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>A mock plan records planned and actual times per task and per object load.</t>
+          <t>A trial-migration plan records planned and actual times per task and per object load.</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>In a mock plan the load of P01 cannot start while C01 is not accepted (reference data and clients first).</t>
+          <t>In a trial-migration plan the load of P01 cannot start while C01 is not accepted (reference data and clients first).</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Client master and reference data. Codes are mapped and created, the PACKAGE map is loaded for the Renewal sanitation, legacy clients are matched, deduplicated and created as active clients; reference data and clients load first in every mock.</t>
+          <t>Client master and reference data. Codes are mapped and created, the PACKAGE map is loaded for the Renewal sanitation, legacy clients are matched, deduplicated and created as active clients; reference data and clients load first in every trial migration.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Cutover. A mock plan is run with reference data and clients first, go / no-go is decided on measured criteria, the January-May 2028 expiries are extracted at go-live with the RAs already sent and the later expiries move by RMEL cohort, and legacy systems are decommissioned on the checklist.</t>
+          <t>Cutover. A trial-migration plan is run with reference data and clients first, go / no-go is decided on measured criteria, the January-May 2028 expiries are extracted at go-live with the RAs already sent and the later expiries move by RMEL cohort, and legacy systems are decommissioned on the checklist.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>All objects loaded in a mock.</t>
+          <t>All objects loaded in a trial migration.</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>Run a mock plan</t>
+          <t>Run a trial-migration plan</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="I160" s="12" t="inlineStr">
         <is>
-          <t>Mock plan with C01 LOADED but G6 not signed.
+          <t>Trial-migration plan with C01 LOADED but G6 not signed.
 Data: TD-DM-01 Test users per migration role</t>
         </is>
       </c>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>1. In a mock plan record NO-GO.</t>
+          <t>1. In a trial-migration plan record NO-GO.</t>
         </is>
       </c>
       <c r="K163" s="12" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="J168" s="12" t="inlineStr">
         <is>
-          <t>1. In a mock with MIG_CUTOVER_DATE 3 January 2028, run the Renewal extraction for the business date 10 August 2027 (expiry 28 December 2027).</t>
+          <t>1. In a trial migration with MIG_CUTOVER_DATE 3 January 2028, run the Renewal extraction for the business date 10 August 2027 (expiry 28 December 2027).</t>
         </is>
       </c>
       <c r="K168" s="12" t="inlineStr">
